--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C798DFE-4E6F-4E7C-A387-2181CEFC12D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90EF5E16-4215-4E1A-865F-9BAB354A562A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="521" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="73">
   <si>
     <t>Current version in development</t>
   </si>
@@ -247,6 +247,12 @@
   </si>
   <si>
     <t>Fixed texture sampling (26.3+ only)</t>
+  </si>
+  <si>
+    <t>_11_Beta</t>
+  </si>
+  <si>
+    <t>Renamed resource pack</t>
   </si>
 </sst>
 </file>
@@ -441,7 +447,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -453,7 +459,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -479,11 +484,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="7" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -542,6 +544,15 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -734,7 +745,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K78"/>
+  <dimension ref="A1:K79"/>
   <sheetFormatPr defaultColWidth="27.28515625" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="36.5703125" style="6" customWidth="1"/>
@@ -743,992 +754,1009 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="30"/>
-      <c r="G1" s="24" t="s">
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="26"/>
+      <c r="G1" s="42" t="s">
         <v>66</v>
       </c>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
+      <c r="K1" s="42"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="B2" s="26">
+      <c r="B2" s="22">
         <v>6</v>
       </c>
-      <c r="G2" s="8" t="s">
-        <v>5</v>
+      <c r="G2" s="7" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="B3" s="26">
+      <c r="B3" s="22">
         <v>3</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="K3" s="8" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="26">
+      <c r="B4" s="22">
         <v>9</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="10">
+      <c r="H4" s="9">
         <v>11</v>
       </c>
-      <c r="I4" s="10">
+      <c r="I4" s="9">
         <v>3</v>
       </c>
-      <c r="J4" s="10" t="str">
+      <c r="J4" s="9" t="str">
         <f>D8</f>
         <v>6309-rt6</v>
       </c>
-      <c r="K4" s="10">
+      <c r="K4" s="9">
         <v>26.3</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="23" t="s">
+      <c r="A5" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="B5" s="26">
+      <c r="B5" s="22">
         <v>2026</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="12" t="str">
-        <f>"Classic_Reimagined_11" &amp; G2</f>
-        <v>Classic_Reimagined_11_SE_2.1</v>
-      </c>
-      <c r="I5" s="13"/>
-      <c r="J5" s="14"/>
-      <c r="K5" s="15"/>
+      <c r="H5" s="11" t="str">
+        <f>"DogePack_Classic" &amp; G2</f>
+        <v>DogePack_Classic_11_Beta</v>
+      </c>
+      <c r="I5" s="12"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="14"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="23">
         <f>(B2*1000)+(B3*100)+B4+((B5-2026)*1000)</f>
         <v>6309</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="12" t="str">
+      <c r="H6" s="11" t="str">
         <f>G4 &amp; "." &amp; H4 &amp; "_" &amp; I4 &amp; "-" &amp; H5</f>
-        <v>v10.0.11_3-Classic_Reimagined_11_SE_2.1</v>
-      </c>
-      <c r="I6" s="13"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="15"/>
+        <v>v10.0.11_3-DogePack_Classic_11_Beta</v>
+      </c>
+      <c r="I6" s="12"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="14"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="37" t="s">
+      <c r="A7" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="38"/>
-      <c r="C7" s="39"/>
-      <c r="D7" s="9" t="s">
+      <c r="B7" s="34"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="G7" s="11" t="s">
+      <c r="E7" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="G7" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="12" t="str">
+      <c r="H7" s="11" t="str">
         <f>H6 &amp; "-build-" &amp; J4</f>
-        <v>v10.0.11_3-Classic_Reimagined_11_SE_2.1-build-6309-rt6</v>
-      </c>
-      <c r="I7" s="13"/>
-      <c r="J7" s="14"/>
+        <v>v10.0.11_3-DogePack_Classic_11_Beta-build-6309-rt6</v>
+      </c>
+      <c r="I7" s="12"/>
+      <c r="J7" s="13"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="40" t="str">
+      <c r="A8" s="36" t="str">
         <f>G4 &amp; "." &amp; H4 &amp; "_" &amp; I4 &amp; "-build-" &amp; D8</f>
         <v>v10.0.11_3-build-6309-rt6</v>
       </c>
-      <c r="B8" s="41"/>
-      <c r="C8" s="42"/>
-      <c r="D8" s="10" t="str">
+      <c r="B8" s="37"/>
+      <c r="C8" s="38"/>
+      <c r="D8" s="9" t="str">
         <f>B6&amp;"-rt"&amp;B2</f>
         <v>6309-rt6</v>
       </c>
-      <c r="E8" s="19">
-        <f>K10</f>
+      <c r="E8" s="18">
+        <f>K11</f>
         <v>26.2</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G8" s="42" t="s">
+        <v>66</v>
+      </c>
+      <c r="H8" s="42"/>
+      <c r="I8" s="42"/>
+      <c r="J8" s="42"/>
+      <c r="K8" s="42"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="28"/>
+      <c r="E9" s="29"/>
+      <c r="G9" s="7" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="31" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="32"/>
-      <c r="E9" s="33"/>
-      <c r="G9" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="K9" s="9" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="C10" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="35"/>
-      <c r="E10" s="36"/>
-      <c r="G10" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="H10" s="10">
-        <v>11</v>
-      </c>
-      <c r="I10" s="10">
+      <c r="D10" s="31"/>
+      <c r="E10" s="32"/>
+      <c r="G10" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="J10" s="10" t="str">
-        <f>J4</f>
-        <v>6309-rt6</v>
-      </c>
-      <c r="K10" s="10">
-        <v>26.2</v>
+      <c r="H10" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="G11" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="H11" s="12" t="str">
-        <f>"Classic_Reimagined_11" &amp; G8</f>
-        <v>Classic_Reimagined_11_SE_2.1</v>
-      </c>
-      <c r="I11" s="13"/>
-      <c r="J11" s="14"/>
-      <c r="K11" s="15"/>
+      <c r="G11" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H11" s="9">
+        <v>11</v>
+      </c>
+      <c r="I11" s="9">
+        <v>2</v>
+      </c>
+      <c r="J11" s="9" t="str">
+        <f>J4</f>
+        <v>6309-rt6</v>
+      </c>
+      <c r="K11" s="9">
+        <v>26.2</v>
+      </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="G12" s="11" t="s">
+      <c r="G12" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12" s="11" t="str">
+        <f>"Classic_Reimagined_11" &amp; G9</f>
+        <v>Classic_Reimagined_11_SE_2.1</v>
+      </c>
+      <c r="I12" s="12"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="14"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="G13" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="H12" s="12" t="str">
-        <f>G10 &amp; "." &amp; H10 &amp; "_" &amp; I10 &amp; "-" &amp; H11</f>
+      <c r="H13" s="11" t="str">
+        <f>G11 &amp; "." &amp; H11 &amp; "_" &amp; I11 &amp; "-" &amp; H12</f>
         <v>v10.0.11_2-Classic_Reimagined_11_SE_2.1</v>
       </c>
-      <c r="I12" s="13"/>
-      <c r="J12" s="14"/>
-      <c r="K12" s="15"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="G13" s="11" t="s">
+      <c r="I13" s="12"/>
+      <c r="J13" s="13"/>
+      <c r="K13" s="14"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G14" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="H13" s="12" t="str">
-        <f>H12 &amp; "-build-" &amp; J10</f>
+      <c r="H14" s="11" t="str">
+        <f>H13 &amp; "-build-" &amp; J11</f>
         <v>v10.0.11_2-Classic_Reimagined_11_SE_2.1-build-6309-rt6</v>
       </c>
-      <c r="I13" s="13"/>
-      <c r="J13" s="14"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="G14" s="7" t="s">
+      <c r="I14" s="12"/>
+      <c r="J14" s="13"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G15" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="G15" s="8" t="s">
+      <c r="H15" s="43"/>
+      <c r="I15" s="43"/>
+      <c r="J15" s="43"/>
+      <c r="K15" s="43"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G16" s="7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="G16" s="9" t="s">
+    <row r="17" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G17" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="H16" s="9" t="s">
+      <c r="H17" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="I16" s="9" t="s">
+      <c r="I17" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="J16" s="9" t="s">
+      <c r="J17" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="K16" s="9" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G17" s="10" t="s">
+      <c r="K17" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G18" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="H17" s="10">
+      <c r="H18" s="9">
         <v>11</v>
       </c>
-      <c r="I17" s="10">
+      <c r="I18" s="9">
         <v>1</v>
       </c>
-      <c r="J17" s="10" t="str">
-        <f>J10</f>
+      <c r="J18" s="9" t="str">
+        <f>J11</f>
         <v>6309-rt6</v>
       </c>
-      <c r="K17" s="10">
+      <c r="K18" s="9">
         <v>26.1</v>
       </c>
     </row>
-    <row r="18" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G18" s="11" t="s">
+    <row r="19" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G19" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H18" s="12" t="str">
-        <f>"Classic_Reimagined_10" &amp; G15</f>
+      <c r="H19" s="11" t="str">
+        <f>"Classic_Reimagined_10" &amp; G16</f>
         <v>Classic_Reimagined_10_SE_2.1</v>
       </c>
-      <c r="I18" s="13"/>
-      <c r="J18" s="14"/>
-      <c r="K18" s="15"/>
-    </row>
-    <row r="19" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G19" s="11" t="s">
+      <c r="I19" s="12"/>
+      <c r="J19" s="13"/>
+      <c r="K19" s="14"/>
+    </row>
+    <row r="20" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G20" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="H19" s="12" t="str">
-        <f>G17 &amp; "." &amp; H17 &amp; "_" &amp; I17 &amp; "-" &amp; H18</f>
+      <c r="H20" s="11" t="str">
+        <f>G18 &amp; "." &amp; H18 &amp; "_" &amp; I18 &amp; "-" &amp; H19</f>
         <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1</v>
       </c>
-      <c r="I19" s="13"/>
-      <c r="J19" s="14"/>
-      <c r="K19" s="15"/>
-    </row>
-    <row r="20" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G20" s="11" t="s">
+      <c r="I20" s="12"/>
+      <c r="J20" s="13"/>
+      <c r="K20" s="14"/>
+    </row>
+    <row r="21" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G21" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="H20" s="12" t="str">
-        <f>H19 &amp; "-build-" &amp; J17</f>
+      <c r="H21" s="11" t="str">
+        <f>H20 &amp; "-build-" &amp; J18</f>
         <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1-build-6309-rt6</v>
       </c>
-      <c r="I20" s="13"/>
-      <c r="J20" s="14"/>
-    </row>
-    <row r="21" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G21" s="8" t="s">
+      <c r="I21" s="12"/>
+      <c r="J21" s="13"/>
+    </row>
+    <row r="22" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G22" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G22" s="9" t="s">
+    <row r="23" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G23" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H22" s="9" t="s">
+      <c r="H23" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="I22" s="9" t="s">
+      <c r="I23" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="J22" s="9" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G23" s="10" t="s">
+      <c r="J23" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G24" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="H23" s="10">
+      <c r="H24" s="9">
         <v>10</v>
       </c>
-      <c r="I23" s="10" t="str">
-        <f>J17</f>
+      <c r="I24" s="9" t="str">
+        <f>J18</f>
         <v>6309-rt6</v>
       </c>
-      <c r="J23" s="10" t="s">
+      <c r="J24" s="9" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G24" s="11" t="s">
+    <row r="25" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G25" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H24" s="16" t="str">
-        <f>"Classic_Reimagined_10" &amp; G21</f>
+      <c r="H25" s="15" t="str">
+        <f>"Classic_Reimagined_10" &amp; G22</f>
         <v>Classic_Reimagined_10_SE_2</v>
       </c>
-      <c r="I24" s="17"/>
-      <c r="J24" s="15"/>
-    </row>
-    <row r="25" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G25" s="11" t="s">
+      <c r="I25" s="16"/>
+      <c r="J25" s="14"/>
+    </row>
+    <row r="26" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G26" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="H25" s="16" t="str">
-        <f>G23 &amp; "." &amp; H23 &amp; "-" &amp; H24</f>
+      <c r="H26" s="15" t="str">
+        <f>G24 &amp; "." &amp; H24 &amp; "-" &amp; H25</f>
         <v>v10.0.10-Classic_Reimagined_10_SE_2</v>
       </c>
-      <c r="I25" s="17"/>
-      <c r="J25" s="15"/>
-    </row>
-    <row r="26" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G26" s="11" t="s">
+      <c r="I26" s="16"/>
+      <c r="J26" s="14"/>
+    </row>
+    <row r="27" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G27" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="H26" s="16" t="str">
-        <f>H25 &amp; "-build-" &amp; I23</f>
+      <c r="H27" s="15" t="str">
+        <f>H26 &amp; "-build-" &amp; I24</f>
         <v>v10.0.10-Classic_Reimagined_10_SE_2-build-6309-rt6</v>
       </c>
-      <c r="I26" s="17"/>
-    </row>
-    <row r="27" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G27" s="9" t="s">
+      <c r="I27" s="16"/>
+    </row>
+    <row r="28" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G28" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H27" s="9" t="s">
+      <c r="H28" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="I27" s="9" t="s">
+      <c r="I28" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="J27" s="9" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="28" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G28" s="10" t="s">
+      <c r="J28" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G29" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="H28" s="10">
+      <c r="H29" s="9">
         <v>9</v>
       </c>
-      <c r="I28" s="10" t="str">
-        <f>I23</f>
+      <c r="I29" s="9" t="str">
+        <f>I24</f>
         <v>6309-rt6</v>
       </c>
-      <c r="J28" s="10" t="s">
+      <c r="J29" s="9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G29" s="11" t="s">
+    <row r="30" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G30" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H29" s="16" t="str">
-        <f>H24</f>
+      <c r="H30" s="15" t="str">
+        <f>H25</f>
         <v>Classic_Reimagined_10_SE_2</v>
       </c>
-      <c r="I29" s="17"/>
-      <c r="J29" s="15"/>
-    </row>
-    <row r="30" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G30" s="11" t="s">
+      <c r="I30" s="16"/>
+      <c r="J30" s="14"/>
+    </row>
+    <row r="31" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G31" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="H30" s="16" t="str">
-        <f>G28 &amp; "." &amp; H28 &amp; "-" &amp; H29</f>
+      <c r="H31" s="15" t="str">
+        <f>G29 &amp; "." &amp; H29 &amp; "-" &amp; H30</f>
         <v>v10.0.9-Classic_Reimagined_10_SE_2</v>
       </c>
-      <c r="I30" s="17"/>
-      <c r="J30" s="15"/>
-    </row>
-    <row r="31" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G31" s="11" t="s">
+      <c r="I31" s="16"/>
+      <c r="J31" s="14"/>
+    </row>
+    <row r="32" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G32" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="H31" s="16" t="str">
-        <f>H30 &amp; "-build-" &amp; I28</f>
+      <c r="H32" s="15" t="str">
+        <f>H31 &amp; "-build-" &amp; I29</f>
         <v>v10.0.9-Classic_Reimagined_10_SE_2-build-6309-rt6</v>
       </c>
-      <c r="I31" s="17"/>
-    </row>
-    <row r="32" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G32" s="9" t="s">
+      <c r="I32" s="16"/>
+    </row>
+    <row r="33" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G33" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H32" s="9" t="s">
+      <c r="H33" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="I32" s="9" t="s">
+      <c r="I33" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="J32" s="9" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G33" s="10" t="s">
+      <c r="J33" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G34" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="H33" s="10">
+      <c r="H34" s="9">
         <v>7</v>
       </c>
-      <c r="I33" s="10" t="str">
-        <f>I28</f>
+      <c r="I34" s="9" t="str">
+        <f>I29</f>
         <v>6309-rt6</v>
       </c>
-      <c r="J33" s="10" t="s">
+      <c r="J34" s="9" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G34" s="11" t="s">
+    <row r="35" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G35" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H34" s="16" t="str">
-        <f>H29</f>
+      <c r="H35" s="15" t="str">
+        <f>H30</f>
         <v>Classic_Reimagined_10_SE_2</v>
       </c>
-      <c r="I34" s="17"/>
-      <c r="J34" s="15"/>
-    </row>
-    <row r="35" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G35" s="11" t="s">
+      <c r="I35" s="16"/>
+      <c r="J35" s="14"/>
+    </row>
+    <row r="36" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G36" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="H35" s="16" t="str">
-        <f>G33 &amp; "." &amp; H33 &amp; "-" &amp; H34</f>
+      <c r="H36" s="15" t="str">
+        <f>G34 &amp; "." &amp; H34 &amp; "-" &amp; H35</f>
         <v>v10.0.7-Classic_Reimagined_10_SE_2</v>
       </c>
-      <c r="I35" s="17"/>
-      <c r="J35" s="15"/>
-    </row>
-    <row r="36" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G36" s="11" t="s">
+      <c r="I36" s="16"/>
+      <c r="J36" s="14"/>
+    </row>
+    <row r="37" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G37" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="H36" s="16" t="str">
-        <f>H35 &amp; "-build-" &amp; I33</f>
+      <c r="H37" s="15" t="str">
+        <f>H36 &amp; "-build-" &amp; I34</f>
         <v>v10.0.7-Classic_Reimagined_10_SE_2-build-6309-rt6</v>
       </c>
-      <c r="I36" s="17"/>
-    </row>
-    <row r="37" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G37" s="9" t="s">
+      <c r="I37" s="16"/>
+    </row>
+    <row r="38" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G38" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H37" s="9" t="s">
+      <c r="H38" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="I37" s="9" t="s">
+      <c r="I38" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="J37" s="9" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="38" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G38" s="10" t="s">
+      <c r="J38" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G39" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="H38" s="10">
-        <v>4</v>
-      </c>
-      <c r="I38" s="10" t="str">
-        <f>I33</f>
+      <c r="H39" s="9">
+        <v>4</v>
+      </c>
+      <c r="I39" s="9" t="str">
+        <f>I34</f>
         <v>6309-rt6</v>
       </c>
-      <c r="J38" s="10" t="s">
+      <c r="J39" s="9" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="39" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G39" s="11" t="s">
+    <row r="40" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G40" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H39" s="16" t="str">
-        <f>H34</f>
+      <c r="H40" s="15" t="str">
+        <f>H35</f>
         <v>Classic_Reimagined_10_SE_2</v>
       </c>
-      <c r="I39" s="17"/>
-      <c r="J39" s="15"/>
-    </row>
-    <row r="40" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G40" s="11" t="s">
+      <c r="I40" s="16"/>
+      <c r="J40" s="14"/>
+    </row>
+    <row r="41" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G41" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="H40" s="16" t="str">
-        <f>G38 &amp; "." &amp; H38 &amp; "-" &amp; H39</f>
+      <c r="H41" s="15" t="str">
+        <f>G39 &amp; "." &amp; H39 &amp; "-" &amp; H40</f>
         <v>v10.0.4-Classic_Reimagined_10_SE_2</v>
       </c>
-      <c r="I40" s="17"/>
-      <c r="J40" s="15"/>
-    </row>
-    <row r="41" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G41" s="11" t="s">
+      <c r="I41" s="16"/>
+      <c r="J41" s="14"/>
+    </row>
+    <row r="42" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G42" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="H41" s="16" t="str">
-        <f>H40 &amp; "-build-" &amp; I38</f>
+      <c r="H42" s="15" t="str">
+        <f>H41 &amp; "-build-" &amp; I39</f>
         <v>v10.0.4-Classic_Reimagined_10_SE_2-build-6309-rt6</v>
       </c>
-      <c r="I41" s="17"/>
-    </row>
-    <row r="42" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G42" s="8" t="s">
+      <c r="I42" s="16"/>
+    </row>
+    <row r="43" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G43" s="7" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="43" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G43" s="9" t="s">
+    <row r="44" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G44" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H43" s="9" t="s">
+      <c r="H44" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="I43" s="9" t="s">
+      <c r="I44" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="J43" s="9" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="44" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G44" s="10" t="s">
+      <c r="J44" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G45" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="H44" s="10">
+      <c r="H45" s="9">
         <v>3</v>
       </c>
-      <c r="I44" s="10" t="str">
-        <f>I38</f>
+      <c r="I45" s="9" t="str">
+        <f>I39</f>
         <v>6309-rt6</v>
       </c>
-      <c r="J44" s="10" t="s">
+      <c r="J45" s="9" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="45" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G45" s="11" t="s">
+    <row r="46" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G46" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H45" s="16" t="str">
-        <f>"Classic_Reimagined_10" &amp; G42</f>
+      <c r="H46" s="15" t="str">
+        <f>"Classic_Reimagined_10" &amp; G43</f>
         <v>Classic_Reimagined_10_SE</v>
       </c>
-      <c r="I45" s="17"/>
-      <c r="J45" s="15"/>
-    </row>
-    <row r="46" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G46" s="11" t="s">
+      <c r="I46" s="16"/>
+      <c r="J46" s="14"/>
+    </row>
+    <row r="47" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G47" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="H46" s="16" t="str">
-        <f>G44 &amp; "." &amp; H44 &amp; "-" &amp; H45</f>
+      <c r="H47" s="15" t="str">
+        <f>G45 &amp; "." &amp; H45 &amp; "-" &amp; H46</f>
         <v>v10.0.3-Classic_Reimagined_10_SE</v>
       </c>
-      <c r="I46" s="17"/>
-      <c r="J46" s="15"/>
-    </row>
-    <row r="47" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G47" s="11" t="s">
+      <c r="I47" s="16"/>
+      <c r="J47" s="14"/>
+    </row>
+    <row r="48" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G48" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="H47" s="16" t="str">
-        <f>H46 &amp; "-build-" &amp; I44</f>
+      <c r="H48" s="15" t="str">
+        <f>H47 &amp; "-build-" &amp; I45</f>
         <v>v10.0.3-Classic_Reimagined_10_SE-build-6309-rt6</v>
       </c>
-      <c r="I47" s="17"/>
-    </row>
-    <row r="48" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G48" s="8" t="s">
+      <c r="I48" s="16"/>
+    </row>
+    <row r="49" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G49" s="7" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="49" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G49" s="9" t="s">
+    <row r="50" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G50" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H49" s="9" t="s">
+      <c r="H50" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="I49" s="9" t="s">
+      <c r="I50" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="J49" s="9" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="50" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G50" s="10" t="s">
+      <c r="J50" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="51" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G51" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="H50" s="10">
+      <c r="H51" s="9">
         <v>2</v>
       </c>
-      <c r="I50" s="10" t="str">
-        <f>I44</f>
+      <c r="I51" s="9" t="str">
+        <f>I45</f>
         <v>6309-rt6</v>
       </c>
-      <c r="J50" s="10" t="s">
+      <c r="J51" s="9" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="51" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G51" s="11" t="s">
+    <row r="52" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G52" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H51" s="16" t="s">
+      <c r="H52" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="I51" s="17"/>
-      <c r="J51" s="15"/>
-    </row>
-    <row r="52" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G52" s="11" t="s">
+      <c r="I52" s="16"/>
+      <c r="J52" s="14"/>
+    </row>
+    <row r="53" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G53" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="H52" s="16" t="str">
-        <f>G50 &amp; "." &amp; H50 &amp; "-" &amp; H51</f>
+      <c r="H53" s="15" t="str">
+        <f>G51 &amp; "." &amp; H51 &amp; "-" &amp; H52</f>
         <v>v10.0.2-Classic_Reimagined_10s</v>
       </c>
-      <c r="I52" s="17"/>
-      <c r="J52" s="15"/>
-    </row>
-    <row r="53" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G53" s="11" t="s">
+      <c r="I53" s="16"/>
+      <c r="J53" s="14"/>
+    </row>
+    <row r="54" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G54" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="H53" s="16" t="str">
-        <f>H52 &amp; "-build-" &amp; I50</f>
+      <c r="H54" s="15" t="str">
+        <f>H53 &amp; "-build-" &amp; I51</f>
         <v>v10.0.2-Classic_Reimagined_10s-build-6309-rt6</v>
       </c>
-      <c r="I53" s="17"/>
-    </row>
-    <row r="54" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G54" s="8" t="s">
+      <c r="I54" s="16"/>
+    </row>
+    <row r="55" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G55" s="7" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="55" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G55" s="9" t="s">
+    <row r="56" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G56" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H55" s="9" t="s">
+      <c r="H56" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="I55" s="9" t="s">
+      <c r="I56" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="J55" s="9" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="56" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G56" s="10" t="s">
+      <c r="J56" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G57" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="H56" s="10">
+      <c r="H57" s="9">
         <v>1</v>
       </c>
-      <c r="I56" s="10" t="str">
-        <f>I50</f>
+      <c r="I57" s="9" t="str">
+        <f>I51</f>
         <v>6309-rt6</v>
       </c>
-      <c r="J56" s="10" t="s">
+      <c r="J57" s="9" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="57" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G57" s="11" t="s">
+    <row r="58" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G58" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H57" s="16" t="s">
+      <c r="H58" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="I57" s="17"/>
-      <c r="J57" s="15"/>
-    </row>
-    <row r="58" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G58" s="11" t="s">
+      <c r="I58" s="16"/>
+      <c r="J58" s="14"/>
+    </row>
+    <row r="59" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G59" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="H58" s="16" t="str">
-        <f>G56 &amp; "." &amp; H56 &amp; "-" &amp; H57</f>
+      <c r="H59" s="15" t="str">
+        <f>G57 &amp; "." &amp; H57 &amp; "-" &amp; H58</f>
         <v>v10.0.1-Classic_Reimagined_10</v>
       </c>
-      <c r="I58" s="17"/>
-      <c r="J58" s="15"/>
-    </row>
-    <row r="59" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G59" s="11" t="s">
+      <c r="I59" s="16"/>
+      <c r="J59" s="14"/>
+    </row>
+    <row r="60" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G60" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="H59" s="16" t="str">
-        <f>H58 &amp; "-build-" &amp; I56</f>
+      <c r="H60" s="15" t="str">
+        <f>H59 &amp; "-build-" &amp; I57</f>
         <v>v10.0.1-Classic_Reimagined_10-build-6309-rt6</v>
       </c>
-      <c r="I59" s="17"/>
-    </row>
-    <row r="60" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G60" s="7" t="s">
+      <c r="I60" s="16"/>
+    </row>
+    <row r="61" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G61" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="H60" s="7"/>
-      <c r="I60" s="7"/>
-      <c r="J60" s="7"/>
-    </row>
-    <row r="61" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G61" s="8" t="s">
+      <c r="H61" s="43"/>
+      <c r="I61" s="43"/>
+      <c r="J61" s="43"/>
+    </row>
+    <row r="62" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G62" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="62" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G62" s="9" t="s">
+    <row r="63" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G63" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H62" s="9" t="s">
+      <c r="H63" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="I62" s="9" t="s">
+      <c r="I63" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="J62" s="9" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="63" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G63" s="10" t="s">
+      <c r="J63" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="64" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G64" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="H63" s="10">
+      <c r="H64" s="9">
         <v>32</v>
       </c>
-      <c r="I63" s="10" t="str">
-        <f>I56</f>
+      <c r="I64" s="9" t="str">
+        <f>I57</f>
         <v>6309-rt6</v>
       </c>
-      <c r="J63" s="10" t="s">
+      <c r="J64" s="9" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="64" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G64" s="11" t="s">
+    <row r="65" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G65" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H64" s="16" t="s">
+      <c r="H65" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="I64" s="17"/>
-      <c r="J64" s="15"/>
-    </row>
-    <row r="65" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G65" s="11" t="s">
+      <c r="I65" s="16"/>
+      <c r="J65" s="14"/>
+    </row>
+    <row r="66" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G66" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="H65" s="16" t="str">
-        <f>G63 &amp; "." &amp; H63 &amp; "-" &amp; H64</f>
+      <c r="H66" s="15" t="str">
+        <f>G64 &amp; "." &amp; H64 &amp; "-" &amp; H65</f>
         <v>v8.10.32-Classic_Reimagined_8</v>
       </c>
-      <c r="I65" s="17"/>
-      <c r="J65" s="15"/>
-    </row>
-    <row r="66" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G66" s="11" t="s">
+      <c r="I66" s="16"/>
+      <c r="J66" s="14"/>
+    </row>
+    <row r="67" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G67" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="H66" s="16" t="str">
-        <f>H65 &amp; "-build-" &amp; I63</f>
+      <c r="H67" s="15" t="str">
+        <f>H66 &amp; "-build-" &amp; I64</f>
         <v>v8.10.32-Classic_Reimagined_8-build-6309-rt6</v>
       </c>
-      <c r="I66" s="17"/>
-    </row>
-    <row r="67" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G67" s="8" t="s">
+      <c r="I67" s="16"/>
+    </row>
+    <row r="68" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G68" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="68" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G68" s="9" t="s">
+    <row r="69" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G69" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H68" s="9" t="s">
+      <c r="H69" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="I68" s="9" t="s">
+      <c r="I69" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="J68" s="9" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="69" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G69" s="10" t="s">
+      <c r="J69" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G70" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="H69" s="10">
+      <c r="H70" s="9">
         <v>31</v>
       </c>
-      <c r="I69" s="10" t="str">
-        <f>I63</f>
+      <c r="I70" s="9" t="str">
+        <f>I64</f>
         <v>6309-rt6</v>
       </c>
-      <c r="J69" s="10" t="s">
+      <c r="J70" s="9" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="70" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G70" s="11" t="s">
+    <row r="71" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G71" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H70" s="16" t="s">
+      <c r="H71" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="I70" s="17"/>
-      <c r="J70" s="15"/>
-    </row>
-    <row r="71" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G71" s="11" t="s">
+      <c r="I71" s="16"/>
+      <c r="J71" s="14"/>
+    </row>
+    <row r="72" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G72" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="H71" s="16" t="str">
-        <f>G69 &amp; "." &amp; H69 &amp; "-" &amp; H70</f>
+      <c r="H72" s="15" t="str">
+        <f>G70 &amp; "." &amp; H70 &amp; "-" &amp; H71</f>
         <v>v8.10.31-Classic_Reimagined_8</v>
       </c>
-      <c r="I71" s="17"/>
-      <c r="J71" s="15"/>
-    </row>
-    <row r="72" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G72" s="11" t="s">
+      <c r="I72" s="16"/>
+      <c r="J72" s="14"/>
+    </row>
+    <row r="73" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G73" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="H72" s="16" t="str">
-        <f>H71 &amp; "-build-" &amp; I69</f>
+      <c r="H73" s="15" t="str">
+        <f>H72 &amp; "-build-" &amp; I70</f>
         <v>v8.10.31-Classic_Reimagined_8-build-6309-rt6</v>
       </c>
-      <c r="I72" s="17"/>
-    </row>
-    <row r="73" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G73" s="21" t="s">
+      <c r="I73" s="16"/>
+    </row>
+    <row r="74" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G74" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="H73" s="21"/>
-      <c r="I73" s="21"/>
-      <c r="J73" s="21"/>
-    </row>
-    <row r="74" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G74" s="9" t="s">
+      <c r="H74" s="44"/>
+      <c r="I74" s="44"/>
+      <c r="J74" s="44"/>
+    </row>
+    <row r="75" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G75" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H74" s="9" t="s">
+      <c r="H75" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="I74" s="9" t="s">
+      <c r="I75" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="J74" s="9" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="75" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G75" s="10" t="s">
+      <c r="J75" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G76" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="H75" s="10">
+      <c r="H76" s="9">
         <v>3</v>
       </c>
-      <c r="I75" s="10" t="str">
-        <f>I69</f>
+      <c r="I76" s="9" t="str">
+        <f>I70</f>
         <v>6309-rt6</v>
       </c>
-      <c r="J75" s="10" t="s">
+      <c r="J76" s="9" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="76" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G76" s="11" t="s">
+    <row r="77" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G77" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H76" s="16" t="s">
+      <c r="H77" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="I76" s="17"/>
-      <c r="J76" s="15"/>
-    </row>
-    <row r="77" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G77" s="11" t="s">
+      <c r="I77" s="16"/>
+      <c r="J77" s="14"/>
+    </row>
+    <row r="78" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G78" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="H77" s="16" t="str">
-        <f>G75 &amp; "." &amp; H75 &amp; "-" &amp; H76</f>
+      <c r="H78" s="15" t="str">
+        <f>G76 &amp; "." &amp; H76 &amp; "-" &amp; H77</f>
         <v>v7.11.3-Better_Default_7</v>
       </c>
-      <c r="I77" s="17"/>
-      <c r="J77" s="15"/>
-    </row>
-    <row r="78" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G78" s="11" t="s">
+      <c r="I78" s="16"/>
+      <c r="J78" s="14"/>
+    </row>
+    <row r="79" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G79" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="H78" s="16" t="str">
-        <f>H77 &amp; "-build-" &amp; I75</f>
+      <c r="H79" s="15" t="str">
+        <f>H78 &amp; "-build-" &amp; I76</f>
         <v>v7.11.3-Better_Default_7-build-6309-rt6</v>
       </c>
-      <c r="I78" s="17"/>
+      <c r="I79" s="16"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A10:A20">
     <sortCondition ref="A20"/>
   </sortState>
-  <mergeCells count="5">
+  <mergeCells count="10">
+    <mergeCell ref="G74:J74"/>
+    <mergeCell ref="G1:K1"/>
+    <mergeCell ref="G15:K15"/>
+    <mergeCell ref="G61:J61"/>
+    <mergeCell ref="G8:K8"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="C9:E9"/>
     <mergeCell ref="C10:E10"/>
@@ -1749,12 +1777,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="41" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
     </row>
     <row r="2" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
@@ -1793,21 +1821,21 @@
       <c r="A5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="43" t="s">
+      <c r="B5" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="44"/>
+      <c r="C5" s="40"/>
       <c r="D5" s="5"/>
     </row>
     <row r="6" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="43" t="str">
+      <c r="B6" s="39" t="str">
         <f>A4 &amp; "." &amp; B4 &amp; "." &amp; C4 &amp; "-" &amp; B5</f>
         <v>v6.0.7-Better_Default_6</v>
       </c>
-      <c r="C6" s="44"/>
+      <c r="C6" s="40"/>
       <c r="D6" s="5"/>
     </row>
     <row r="7" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -1847,21 +1875,21 @@
       <c r="A10" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="43" t="s">
+      <c r="B10" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="44"/>
+      <c r="C10" s="40"/>
       <c r="D10" s="5"/>
     </row>
     <row r="11" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="43" t="str">
+      <c r="B11" s="39" t="str">
         <f>A9 &amp; "." &amp; B9 &amp; "." &amp; C9 &amp; "-" &amp; B10</f>
         <v>v1.4.0-Better_Default_5</v>
       </c>
-      <c r="C11" s="44"/>
+      <c r="C11" s="40"/>
       <c r="D11" s="5"/>
     </row>
     <row r="12" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -1901,21 +1929,21 @@
       <c r="A15" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="43" t="s">
+      <c r="B15" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="C15" s="44"/>
+      <c r="C15" s="40"/>
       <c r="D15" s="5"/>
     </row>
     <row r="16" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="43" t="str">
+      <c r="B16" s="39" t="str">
         <f>A14 &amp; "." &amp; B14 &amp; "." &amp; C14 &amp; "-" &amp; B15</f>
         <v>v1.3.0-Better_Default_4</v>
       </c>
-      <c r="C16" s="44"/>
+      <c r="C16" s="40"/>
       <c r="D16" s="5"/>
     </row>
     <row r="17" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -1955,21 +1983,21 @@
       <c r="A20" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="43" t="s">
+      <c r="B20" s="39" t="s">
         <v>55</v>
       </c>
-      <c r="C20" s="44"/>
+      <c r="C20" s="40"/>
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="43" t="str">
+      <c r="B21" s="39" t="str">
         <f>A19 &amp; "." &amp; B19 &amp; "." &amp; C19 &amp; "-" &amp; B20</f>
         <v>v1.2.2-Better_Default_3.1</v>
       </c>
-      <c r="C21" s="44"/>
+      <c r="C21" s="40"/>
       <c r="D21" s="5"/>
     </row>
     <row r="22" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2009,21 +2037,21 @@
       <c r="A25" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B25" s="43" t="s">
+      <c r="B25" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="C25" s="44"/>
+      <c r="C25" s="40"/>
       <c r="D25" s="5"/>
     </row>
     <row r="26" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="43" t="str">
+      <c r="B26" s="39" t="str">
         <f>A24 &amp; "." &amp; B24 &amp; "." &amp; C24 &amp; "-" &amp; B25</f>
         <v>v1.2.1-Better_Default_3</v>
       </c>
-      <c r="C26" s="44"/>
+      <c r="C26" s="40"/>
       <c r="D26" s="5"/>
     </row>
     <row r="27" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2063,21 +2091,21 @@
       <c r="A30" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B30" s="43" t="s">
+      <c r="B30" s="39" t="s">
         <v>58</v>
       </c>
-      <c r="C30" s="44"/>
+      <c r="C30" s="40"/>
       <c r="D30" s="5"/>
     </row>
     <row r="31" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B31" s="43" t="str">
+      <c r="B31" s="39" t="str">
         <f>A29 &amp; "." &amp; B29 &amp; "." &amp; C29 &amp; "-" &amp; B30</f>
         <v>v1.2.0-Better_Default_2</v>
       </c>
-      <c r="C31" s="44"/>
+      <c r="C31" s="40"/>
       <c r="D31" s="5"/>
     </row>
     <row r="32" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2117,21 +2145,21 @@
       <c r="A35" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B35" s="43" t="s">
+      <c r="B35" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="C35" s="44"/>
+      <c r="C35" s="40"/>
       <c r="D35" s="5"/>
     </row>
     <row r="36" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B36" s="43" t="str">
+      <c r="B36" s="39" t="str">
         <f>A34 &amp; "." &amp; B34 &amp; "." &amp; C34 &amp; "-" &amp; B35</f>
         <v>v1.1.1-Better_Default</v>
       </c>
-      <c r="C36" s="44"/>
+      <c r="C36" s="40"/>
       <c r="D36" s="5"/>
     </row>
     <row r="37" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2171,25 +2199,30 @@
       <c r="A40" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B40" s="43" t="s">
+      <c r="B40" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="C40" s="44"/>
+      <c r="C40" s="40"/>
       <c r="D40" s="5"/>
     </row>
     <row r="41" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B41" s="43" t="str">
+      <c r="B41" s="39" t="str">
         <f>A39 &amp; "." &amp; B39 &amp; "." &amp; C39 &amp; "-" &amp; B40</f>
         <v>v1.1.0-Better_Default</v>
       </c>
-      <c r="C41" s="44"/>
+      <c r="C41" s="40"/>
       <c r="D41" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
@@ -2202,11 +2235,6 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
